--- a/sheet/Way_R1WithoutWild.xlsx
+++ b/sheet/Way_R1WithoutWild.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13965" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13965" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Reel" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="17">
   <si>
     <t>R1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -159,7 +159,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -183,6 +183,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -935,6 +941,20 @@
         <v>50</v>
       </c>
     </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="11">
+        <v>50</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0</v>
+      </c>
+    </row>
     <row r="12" spans="1:11">
       <c r="K12" s="2"/>
     </row>
